--- a/backend/public/payrolltemplate.xlsx
+++ b/backend/public/payrolltemplate.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron\OneDrive\Documents\GitHub\springboard-hrs\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4F9167-5DAB-4A67-A376-44AB9927833B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003B6C9B-F956-476B-AE27-59C4652BFD25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1116" yWindow="2100" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Payslip" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="42">
   <si>
     <t>Employee Details</t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>Incentives / Others</t>
+  </si>
+  <si>
+    <t>Bank Account Num:</t>
   </si>
 </sst>
 </file>
@@ -557,6 +560,19 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -566,16 +582,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -586,10 +592,6 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -597,6 +599,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -997,14 +1000,14 @@
       <c r="F5" s="57"/>
       <c r="G5" s="57"/>
       <c r="H5" s="55"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="54"/>
       <c r="Q5" s="8"/>
       <c r="R5" s="1"/>
     </row>
@@ -1016,15 +1019,15 @@
       <c r="E6" s="57"/>
       <c r="F6" s="57"/>
       <c r="G6" s="57"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
-      <c r="P6" s="45"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="54"/>
+      <c r="P6" s="54"/>
       <c r="Q6" s="8"/>
       <c r="R6" s="1"/>
     </row>
@@ -1040,11 +1043,11 @@
       <c r="I7" s="11"/>
       <c r="J7" s="11"/>
       <c r="K7" s="56"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
-      <c r="P7" s="45"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="54"/>
+      <c r="N7" s="54"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="54"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="1"/>
     </row>
@@ -1094,85 +1097,85 @@
       <c r="C10" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
       <c r="J10" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="K10" s="45"/>
+      <c r="K10" s="54"/>
       <c r="L10" s="60"/>
-      <c r="M10" s="45"/>
-      <c r="N10" s="45"/>
-      <c r="O10" s="45"/>
-      <c r="P10" s="45"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
       <c r="Q10" s="19"/>
       <c r="R10" s="1"/>
     </row>
     <row r="11" spans="1:18" ht="26.25" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="16"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="45"/>
-      <c r="M11" s="45"/>
-      <c r="N11" s="45"/>
-      <c r="O11" s="45"/>
-      <c r="P11" s="45"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
       <c r="Q11" s="19"/>
       <c r="R11" s="1"/>
     </row>
     <row r="12" spans="1:18" ht="6" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="20"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="45"/>
-      <c r="N12" s="45"/>
-      <c r="O12" s="45"/>
-      <c r="P12" s="45"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="54"/>
+      <c r="K12" s="54"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="54"/>
+      <c r="N12" s="54"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="54"/>
       <c r="Q12" s="19"/>
       <c r="R12" s="1"/>
     </row>
     <row r="13" spans="1:18" ht="16.2" thickBot="1">
       <c r="A13" s="1"/>
       <c r="B13" s="21"/>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="51"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="52"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="51"/>
       <c r="I13" s="22"/>
-      <c r="J13" s="50" t="s">
+      <c r="J13" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="K13" s="51"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="45"/>
+      <c r="M13" s="45"/>
+      <c r="N13" s="45"/>
+      <c r="O13" s="45"/>
+      <c r="P13" s="46"/>
       <c r="Q13" s="19"/>
       <c r="R13" s="1"/>
     </row>
@@ -1199,24 +1202,24 @@
     <row r="15" spans="1:18" ht="16.2" thickBot="1">
       <c r="A15" s="1"/>
       <c r="B15" s="21"/>
-      <c r="C15" s="50" t="s">
+      <c r="C15" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="51"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="52"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="51"/>
       <c r="I15" s="22"/>
-      <c r="J15" s="50" t="s">
+      <c r="J15" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="K15" s="51"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="45"/>
+      <c r="M15" s="45"/>
+      <c r="N15" s="45"/>
+      <c r="O15" s="45"/>
+      <c r="P15" s="46"/>
       <c r="Q15" s="19"/>
       <c r="R15" s="1"/>
     </row>
@@ -1243,24 +1246,24 @@
     <row r="17" spans="1:18" ht="16.2" thickBot="1">
       <c r="A17" s="1"/>
       <c r="B17" s="21"/>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="51"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="52"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="51"/>
       <c r="I17" s="22"/>
-      <c r="J17" s="53" t="s">
+      <c r="J17" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="K17" s="51"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="40"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="40"/>
-      <c r="P17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="45"/>
+      <c r="M17" s="45"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="45"/>
+      <c r="P17" s="46"/>
       <c r="Q17" s="19"/>
       <c r="R17" s="1"/>
     </row>
@@ -1287,19 +1290,19 @@
     <row r="19" spans="1:18" ht="16.2" thickBot="1">
       <c r="A19" s="1"/>
       <c r="B19" s="21"/>
-      <c r="C19" s="50" t="s">
+      <c r="C19" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="51"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="52"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="51"/>
       <c r="I19" s="22"/>
-      <c r="J19" s="50" t="s">
+      <c r="J19" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="K19" s="51"/>
+      <c r="K19" s="41"/>
       <c r="L19" s="42"/>
       <c r="M19" s="42"/>
       <c r="N19" s="42"/>
@@ -1328,27 +1331,23 @@
       <c r="Q20" s="19"/>
       <c r="R20" s="1"/>
     </row>
-    <row r="21" spans="1:18" ht="15.6">
+    <row r="21" spans="1:18" ht="16.2" thickBot="1">
       <c r="A21" s="1"/>
       <c r="B21" s="25"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="45"/>
-      <c r="M21" s="45"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="45"/>
-      <c r="P21" s="45"/>
+      <c r="C21" s="39"/>
+      <c r="J21" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="42"/>
+      <c r="P21" s="43"/>
       <c r="Q21" s="19"/>
       <c r="R21" s="1"/>
     </row>
-    <row r="22" spans="1:18" ht="15.6">
+    <row r="22" spans="1:18" ht="16.2" thickTop="1">
       <c r="A22" s="1"/>
       <c r="B22" s="25"/>
       <c r="C22" s="34"/>
@@ -1358,92 +1357,92 @@
     <row r="23" spans="1:18" ht="15" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="25"/>
-      <c r="C23" s="48" t="s">
+      <c r="C23" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="48"/>
-      <c r="J23" s="48" t="s">
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="J23" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="K23" s="48"/>
-      <c r="L23" s="48"/>
-      <c r="M23" s="48"/>
-      <c r="N23" s="48"/>
-      <c r="O23" s="48"/>
-      <c r="P23" s="48"/>
+      <c r="K23" s="49"/>
+      <c r="L23" s="49"/>
+      <c r="M23" s="49"/>
+      <c r="N23" s="49"/>
+      <c r="O23" s="49"/>
+      <c r="P23" s="49"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="1"/>
     </row>
     <row r="24" spans="1:18" ht="15" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="25"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48"/>
-      <c r="J24" s="48"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="48"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="48"/>
-      <c r="O24" s="48"/>
-      <c r="P24" s="48"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="49"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="49"/>
+      <c r="L24" s="49"/>
+      <c r="M24" s="49"/>
+      <c r="N24" s="49"/>
+      <c r="O24" s="49"/>
+      <c r="P24" s="49"/>
       <c r="Q24" s="19"/>
       <c r="R24" s="1"/>
     </row>
     <row r="25" spans="1:18" ht="15.6">
       <c r="A25" s="1"/>
       <c r="B25" s="26"/>
-      <c r="C25" s="46" t="s">
+      <c r="C25" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="49" t="s">
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="46" t="s">
+      <c r="G25" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="H25" s="47"/>
-      <c r="J25" s="46" t="s">
+      <c r="H25" s="48"/>
+      <c r="J25" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="K25" s="47"/>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="49" t="s">
+      <c r="K25" s="48"/>
+      <c r="L25" s="48"/>
+      <c r="M25" s="48"/>
+      <c r="N25" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="O25" s="46" t="s">
+      <c r="O25" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="P25" s="47"/>
+      <c r="P25" s="48"/>
       <c r="Q25" s="19"/>
       <c r="R25" s="1"/>
     </row>
     <row r="26" spans="1:18" ht="15.6">
       <c r="A26" s="1"/>
       <c r="B26" s="26"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="49"/>
-      <c r="O26" s="47"/>
-      <c r="P26" s="47"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="48"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="48"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="50"/>
+      <c r="O26" s="48"/>
+      <c r="P26" s="48"/>
       <c r="Q26" s="19"/>
       <c r="R26" s="1"/>
     </row>
@@ -1488,8 +1487,8 @@
       <c r="L28" s="71"/>
       <c r="M28" s="71"/>
       <c r="N28" s="36"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="39"/>
+      <c r="O28" s="44"/>
+      <c r="P28" s="44"/>
       <c r="Q28" s="19"/>
       <c r="R28" s="1"/>
     </row>
@@ -1511,8 +1510,8 @@
       <c r="L29" s="71"/>
       <c r="M29" s="71"/>
       <c r="N29" s="36"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="39"/>
+      <c r="O29" s="44"/>
+      <c r="P29" s="44"/>
       <c r="Q29" s="19"/>
       <c r="R29" s="1"/>
     </row>
@@ -1534,8 +1533,8 @@
       <c r="L30" s="71"/>
       <c r="M30" s="71"/>
       <c r="N30" s="36"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="39"/>
+      <c r="O30" s="44"/>
+      <c r="P30" s="44"/>
       <c r="Q30" s="19"/>
       <c r="R30" s="1"/>
     </row>
@@ -1557,8 +1556,8 @@
       <c r="L31" s="71"/>
       <c r="M31" s="71"/>
       <c r="N31" s="36"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="39"/>
+      <c r="O31" s="44"/>
+      <c r="P31" s="44"/>
       <c r="Q31" s="19"/>
       <c r="R31" s="1"/>
     </row>
@@ -1580,7 +1579,7 @@
       <c r="L32" s="72"/>
       <c r="M32" s="72"/>
       <c r="N32" s="37"/>
-      <c r="O32" s="39"/>
+      <c r="O32" s="44"/>
       <c r="P32" s="72"/>
       <c r="Q32" s="19"/>
       <c r="R32" s="1"/>
@@ -1603,8 +1602,8 @@
       <c r="L33" s="75"/>
       <c r="M33" s="75"/>
       <c r="N33" s="37"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="39"/>
+      <c r="O33" s="44"/>
+      <c r="P33" s="44"/>
       <c r="Q33" s="19"/>
       <c r="R33" s="1"/>
     </row>
@@ -1626,8 +1625,8 @@
       <c r="L34" s="75"/>
       <c r="M34" s="75"/>
       <c r="N34" s="37"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="39"/>
+      <c r="O34" s="44"/>
+      <c r="P34" s="44"/>
       <c r="Q34" s="19"/>
       <c r="R34" s="1"/>
     </row>
@@ -1649,8 +1648,8 @@
       <c r="L35" s="75"/>
       <c r="M35" s="75"/>
       <c r="N35" s="37"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="39"/>
+      <c r="O35" s="44"/>
+      <c r="P35" s="44"/>
       <c r="Q35" s="19"/>
       <c r="R35" s="1"/>
     </row>
@@ -1681,18 +1680,18 @@
       <c r="A37" s="1"/>
       <c r="B37" s="25"/>
       <c r="C37" s="63"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
+      <c r="D37" s="54"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
       <c r="H37" s="63"/>
-      <c r="I37" s="45"/>
+      <c r="I37" s="54"/>
       <c r="J37" s="63"/>
-      <c r="K37" s="45"/>
-      <c r="L37" s="45"/>
-      <c r="M37" s="45"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="54"/>
+      <c r="M37" s="54"/>
       <c r="O37" s="63"/>
-      <c r="P37" s="45"/>
+      <c r="P37" s="54"/>
       <c r="Q37" s="19"/>
       <c r="R37" s="1"/>
     </row>
@@ -1700,18 +1699,18 @@
       <c r="A38" s="1"/>
       <c r="B38" s="25"/>
       <c r="C38" s="63"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="45"/>
-      <c r="F38" s="45"/>
-      <c r="G38" s="45"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
       <c r="H38" s="63"/>
-      <c r="I38" s="45"/>
+      <c r="I38" s="54"/>
       <c r="J38" s="63"/>
-      <c r="K38" s="45"/>
-      <c r="L38" s="45"/>
-      <c r="M38" s="45"/>
+      <c r="K38" s="54"/>
+      <c r="L38" s="54"/>
+      <c r="M38" s="54"/>
       <c r="O38" s="63"/>
-      <c r="P38" s="45"/>
+      <c r="P38" s="54"/>
       <c r="Q38" s="19"/>
       <c r="R38" s="1"/>
     </row>
@@ -1724,8 +1723,8 @@
       <c r="D39" s="70"/>
       <c r="E39" s="70"/>
       <c r="F39" s="70"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
       <c r="J39" s="70" t="s">
         <v>6</v>
       </c>
@@ -1734,7 +1733,7 @@
       <c r="M39" s="70"/>
       <c r="N39" s="70"/>
       <c r="O39" s="69"/>
-      <c r="P39" s="45"/>
+      <c r="P39" s="54"/>
       <c r="Q39" s="19"/>
       <c r="R39" s="1"/>
     </row>
@@ -1744,18 +1743,18 @@
       <c r="C40" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="45"/>
-      <c r="H40" s="45"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="45"/>
-      <c r="K40" s="45"/>
-      <c r="L40" s="45"/>
-      <c r="M40" s="45"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="54"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="54"/>
+      <c r="I40" s="54"/>
+      <c r="J40" s="54"/>
+      <c r="K40" s="54"/>
+      <c r="L40" s="54"/>
+      <c r="M40" s="54"/>
       <c r="O40" s="67"/>
-      <c r="P40" s="45"/>
+      <c r="P40" s="54"/>
       <c r="Q40" s="19"/>
       <c r="R40" s="1"/>
     </row>
@@ -1783,19 +1782,19 @@
       <c r="A42" s="1"/>
       <c r="B42" s="25"/>
       <c r="C42" s="63"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="45"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="45"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="45"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="45"/>
-      <c r="M42" s="45"/>
-      <c r="N42" s="45"/>
-      <c r="O42" s="45"/>
-      <c r="P42" s="45"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="54"/>
+      <c r="K42" s="54"/>
+      <c r="L42" s="54"/>
+      <c r="M42" s="54"/>
+      <c r="N42" s="54"/>
+      <c r="O42" s="54"/>
+      <c r="P42" s="54"/>
       <c r="Q42" s="19"/>
       <c r="R42" s="1"/>
     </row>
@@ -1805,7 +1804,7 @@
       <c r="C43" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="45"/>
+      <c r="D43" s="54"/>
       <c r="E43" s="61"/>
       <c r="F43" s="61"/>
       <c r="G43" s="62"/>
@@ -1814,7 +1813,7 @@
       <c r="J43" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="K43" s="45"/>
+      <c r="K43" s="54"/>
       <c r="L43" s="61"/>
       <c r="M43" s="62"/>
       <c r="N43" s="62"/>
@@ -1827,19 +1826,19 @@
       <c r="A44" s="1"/>
       <c r="B44" s="25"/>
       <c r="C44" s="63"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="45"/>
-      <c r="F44" s="45"/>
-      <c r="G44" s="45"/>
-      <c r="H44" s="45"/>
-      <c r="I44" s="45"/>
-      <c r="J44" s="45"/>
-      <c r="K44" s="45"/>
-      <c r="L44" s="45"/>
-      <c r="M44" s="45"/>
-      <c r="N44" s="45"/>
-      <c r="O44" s="45"/>
-      <c r="P44" s="45"/>
+      <c r="D44" s="54"/>
+      <c r="E44" s="54"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="54"/>
+      <c r="I44" s="54"/>
+      <c r="J44" s="54"/>
+      <c r="K44" s="54"/>
+      <c r="L44" s="54"/>
+      <c r="M44" s="54"/>
+      <c r="N44" s="54"/>
+      <c r="O44" s="54"/>
+      <c r="P44" s="54"/>
       <c r="Q44" s="19"/>
       <c r="R44" s="1"/>
     </row>
@@ -1886,11 +1885,11 @@
     <row r="47" spans="1:18" ht="25.5" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="65"/>
-      <c r="C47" s="45"/>
-      <c r="D47" s="45"/>
-      <c r="E47" s="45"/>
-      <c r="F47" s="45"/>
-      <c r="G47" s="45"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
       <c r="H47" s="33"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -1924,10 +1923,7 @@
       <c r="R48" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="94">
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="J34:M34"/>
+  <mergeCells count="95">
     <mergeCell ref="C33:E33"/>
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="C35:E35"/>
@@ -1990,26 +1986,18 @@
     <mergeCell ref="C10:G11"/>
     <mergeCell ref="J10:K11"/>
     <mergeCell ref="L10:P11"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="C19:D19"/>
     <mergeCell ref="C12:P12"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="E13:H13"/>
     <mergeCell ref="J13:K13"/>
     <mergeCell ref="L13:P13"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="O35:P35"/>
     <mergeCell ref="L15:P15"/>
     <mergeCell ref="L17:P17"/>
     <mergeCell ref="L19:P19"/>
-    <mergeCell ref="C21:P21"/>
     <mergeCell ref="C25:E26"/>
     <mergeCell ref="G25:H26"/>
     <mergeCell ref="J25:M26"/>
@@ -2019,6 +2007,18 @@
     <mergeCell ref="J23:P24"/>
     <mergeCell ref="N25:N26"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:P21"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="J34:M34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
